--- a/AAII_Financials/Yearly/TCEHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCEHY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,136 +653,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>90457300</v>
+      </c>
+      <c r="E8" s="3">
         <v>85886800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>80402500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>88171500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>73838800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>54185600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45464900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>36540800</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>42609500</v>
+      </c>
+      <c r="E9" s="3">
         <v>44550500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45767100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49458000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39892200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30117500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24801000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18570900</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>47847800</v>
+      </c>
+      <c r="E10" s="3">
         <v>41336400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>34635400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38713400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>33946600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24068100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20663900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17969900</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -794,35 +806,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9684200</v>
+      </c>
+      <c r="E12" s="3">
         <v>9036700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8902300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8166700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5969400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4364100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3334800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2682800</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -847,63 +863,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-1198900</v>
+      </c>
+      <c r="E14" s="3">
         <v>1264000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-16852300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-22110600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-7679000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2002900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2048900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1648100</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3268300</v>
+      </c>
+      <c r="E15" s="3">
         <v>2960100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3395100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3643400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2953900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1893600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1279900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>845400</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -912,62 +937,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>61946700</v>
+      </c>
+      <c r="E17" s="3">
         <v>62907100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>64326400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>68675500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>54633800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40194300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34080100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25179400</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>28510600</v>
+      </c>
+      <c r="E18" s="3">
         <v>22979700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16076100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19496000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19205000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13991300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11384800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11361400</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -979,143 +1011,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-2789400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-763900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2246700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2462000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-495400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>230400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-249500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-149500</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>34568400</v>
+      </c>
+      <c r="E21" s="3">
         <v>26703800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17224500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20677400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>22654300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15654500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12914200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12356300</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1705300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1676100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1447700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1246400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1141000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1104400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>712200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>470300</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>33084200</v>
+      </c>
+      <c r="E23" s="3">
         <v>22750800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30479800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39048900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27574400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15711800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13735100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13557600</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>6167600</v>
+      </c>
+      <c r="E24" s="3">
         <v>6103000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3119500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3188000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3047700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1940600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2105600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2419700</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1140,63 +1188,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>26916600</v>
+      </c>
+      <c r="E26" s="3">
         <v>16647800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27360200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35860900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24526700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13771300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11629500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11137900</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>26588600</v>
+      </c>
+      <c r="E27" s="3">
         <v>16248400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27292700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35390600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24484100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13401000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11445500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10990200</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1221,9 +1278,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1248,9 +1308,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1275,9 +1338,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1302,63 +1368,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>2789400</v>
+      </c>
+      <c r="E32" s="3">
         <v>763900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2246700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2462000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>495400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-230400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>249500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>149500</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>26588600</v>
+      </c>
+      <c r="E33" s="3">
         <v>16248400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27292700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35390500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24484100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13401000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11445500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10990200</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1383,68 +1458,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>26588600</v>
+      </c>
+      <c r="E35" s="3">
         <v>16248400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27292700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35390500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24484100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13401000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11445500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10990200</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1456,8 +1540,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1469,251 +1554,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>18155500</v>
+      </c>
+      <c r="E41" s="3">
         <v>24301600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22725000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26440500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23404400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19099900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14221900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16244300</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>28858400</v>
+      </c>
+      <c r="E42" s="3">
         <v>29169100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19430600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15133200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11673700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7812800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10095200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5644000</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>6604000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11320600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10347200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10816200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8108000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5851300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4594900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3162000</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E44" s="3">
         <v>64300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>338300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>167300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>124700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>103100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>47100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>45300</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>13843400</v>
+      </c>
+      <c r="E45" s="3">
         <v>5439600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26505100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20883700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2737000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1730500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1466800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1453100</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>67978200</v>
+      </c>
+      <c r="E46" s="3">
         <v>73114300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>82060700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>76317100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>48654700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36474500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31562900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27425000</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>121035600</v>
+      </c>
+      <c r="E47" s="3">
         <v>101339600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>98499400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>123788800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>109667900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>64834600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>53027000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>42802800</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>15093100</v>
+      </c>
+      <c r="E48" s="3">
         <v>12308600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12429800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13900600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11903200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8847800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5811500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4112700</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>30037100</v>
+      </c>
+      <c r="E49" s="3">
         <v>27486800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26075500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>29768000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26886000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20748400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9270000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6973900</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1738,9 +1851,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1765,36 +1881,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>5977300</v>
+      </c>
+      <c r="E52" s="3">
         <v>3573900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4714200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5294800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3696800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3354900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2674100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2110600</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1819,36 +1941,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>244002000</v>
+      </c>
+      <c r="E54" s="3">
         <v>222432400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>228807500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>253811700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>204243600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137009900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>105198100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>85246300</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1860,8 +1988,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1873,170 +2002,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>16263900</v>
+      </c>
+      <c r="E57" s="3">
         <v>14236300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13394000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17232300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14402800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11588600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10720900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7697500</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>9194000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8722700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4114700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3848700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2766900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5243200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5896400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3142600</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>28366600</v>
+      </c>
+      <c r="E59" s="3">
         <v>19863500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39245600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35561500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18137300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13450400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9527700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9351700</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>54377800</v>
+      </c>
+      <c r="E60" s="3">
         <v>49663200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>62953700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>63454000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41215400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34490800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29433500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23320600</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>39868500</v>
+      </c>
+      <c r="E61" s="3">
         <v>43631700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47955800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47127900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37732000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28221900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20171700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17129600</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1973400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2954500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2122700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2443100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2638700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1195600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1178200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>924600</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2061,9 +2209,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2088,9 +2239,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2115,36 +2269,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>99614900</v>
+      </c>
+      <c r="E66" s="3">
         <v>99220800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>115303500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>115806300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85069100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66805800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53406500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42660500</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2156,8 +2316,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2182,9 +2343,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2209,9 +2373,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2236,9 +2403,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2263,36 +2433,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>122211000</v>
+      </c>
+      <c r="E72" s="3">
         <v>115758800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>103229100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>106230500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>83130200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>55749000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>43975500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>31499100</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2317,9 +2493,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2344,9 +2523,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2371,36 +2553,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>133379200</v>
+      </c>
+      <c r="E76" s="3">
         <v>114032200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>104591900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>126924300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>107830800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62144500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47037500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>39355400</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2425,68 +2613,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>26588600</v>
+      </c>
+      <c r="E81" s="3">
         <v>16248400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27292700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35390500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24484100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13401000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11445500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10990200</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2498,35 +2695,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>3744600</v>
+      </c>
+      <c r="E83" s="3">
         <v>3709700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4124000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4118900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3286800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2243700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1224700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>750000</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2551,9 +2752,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2578,9 +2782,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2605,9 +2812,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2632,9 +2842,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2659,36 +2872,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>35418200</v>
+      </c>
+      <c r="E89" s="3">
         <v>31302400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21181200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27577100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29733600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21340200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16129800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16312400</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2700,35 +2919,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-10516400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2962700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3288100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4612600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5218600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3269600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2870600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1860900</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2753,9 +2976,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2780,36 +3006,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-16740000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17650900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15204900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28106400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27870400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16684100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22087800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14814300</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2821,35 +3053,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>4348900</v>
+      </c>
+      <c r="E96" s="3">
         <v>2959100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1877900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1968200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1583600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1194200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>985200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>776400</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2874,9 +3110,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2901,9 +3140,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2928,88 +3170,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-24180200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11644900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8692400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3403300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2090300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>240100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4490900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4087800</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E101" s="3">
         <v>190800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1088300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-486300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-919600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>155800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>320900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-392100</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-5452900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2197300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1627800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2387700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3033900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5052100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1146200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5193900</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TCEHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCEHY_YR_FIN.xlsx
@@ -739,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>42609500</v>
+        <v>42602400</v>
       </c>
       <c r="E9" s="3">
         <v>44550500</v>
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>47847800</v>
+        <v>47854900</v>
       </c>
       <c r="E10" s="3">
         <v>41336400</v>
@@ -873,10 +873,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-1198900</v>
+        <v>-1218400</v>
       </c>
       <c r="E14" s="3">
-        <v>1264000</v>
+        <v>952100</v>
       </c>
       <c r="F14" s="3">
         <v>-16852300</v>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>3268300</v>
+        <v>3032200</v>
       </c>
       <c r="E15" s="3">
         <v>2960100</v>
@@ -944,10 +944,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>61946700</v>
+        <v>61966100</v>
       </c>
       <c r="E17" s="3">
-        <v>62907100</v>
+        <v>62904700</v>
       </c>
       <c r="F17" s="3">
         <v>64326400</v>
@@ -974,10 +974,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>28510600</v>
+        <v>28491200</v>
       </c>
       <c r="E18" s="3">
-        <v>22979700</v>
+        <v>22982100</v>
       </c>
       <c r="F18" s="3">
         <v>16076100</v>
@@ -1021,7 +1021,7 @@
         <v>-2789400</v>
       </c>
       <c r="E20" s="3">
-        <v>-763900</v>
+        <v>-372600</v>
       </c>
       <c r="F20" s="3">
         <v>2246700</v>
@@ -1048,10 +1048,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>34568400</v>
+        <v>34312700</v>
       </c>
       <c r="E21" s="3">
-        <v>26703800</v>
+        <v>26314900</v>
       </c>
       <c r="F21" s="3">
         <v>17224500</v>
@@ -1381,7 +1381,7 @@
         <v>2789400</v>
       </c>
       <c r="E32" s="3">
-        <v>763900</v>
+        <v>372600</v>
       </c>
       <c r="F32" s="3">
         <v>-2246700</v>
@@ -1621,7 +1621,7 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>6604000</v>
+        <v>11572700</v>
       </c>
       <c r="E43" s="3">
         <v>11320600</v>
@@ -1681,7 +1681,7 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>13843400</v>
+        <v>6499700</v>
       </c>
       <c r="E45" s="3">
         <v>5439600</v>
@@ -1891,7 +1891,7 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>5977300</v>
+        <v>5515100</v>
       </c>
       <c r="E52" s="3">
         <v>3573900</v>
@@ -2069,7 +2069,7 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>28366600</v>
+        <v>22300800</v>
       </c>
       <c r="E59" s="3">
         <v>19863500</v>
@@ -2443,7 +2443,7 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>122211000</v>
+        <v>123357100</v>
       </c>
       <c r="E72" s="3">
         <v>115758800</v>
@@ -2926,7 +2926,7 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-10516400</v>
+        <v>-8621200</v>
       </c>
       <c r="E91" s="3">
         <v>-2962700</v>
@@ -3060,7 +3060,7 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>4348900</v>
+        <v>3953800</v>
       </c>
       <c r="E96" s="3">
         <v>2959100</v>

--- a/AAII_Financials/Yearly/TCEHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TCEHY_YR_FIN.xlsx
@@ -653,148 +653,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>107481100</v>
+      </c>
+      <c r="E8" s="3">
         <v>90457300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>85886800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>80402500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>88171500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>73838800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>54185600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45464900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36540800</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>47022800</v>
+      </c>
+      <c r="E9" s="3">
         <v>42602400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44550500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45767100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49458000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>39892200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30117500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24801000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18570900</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>60458400</v>
+      </c>
+      <c r="E10" s="3">
         <v>47854900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41336400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>34635400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38713400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33946600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24068100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20663900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17969900</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,38 +819,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12259400</v>
+      </c>
+      <c r="E12" s="3">
         <v>9684200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9036700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8902300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8166700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5969400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4364100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3334800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2682800</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -866,69 +882,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-1218400</v>
+        <v>-795400</v>
       </c>
       <c r="E14" s="3">
+        <v>-917400</v>
+      </c>
+      <c r="F14" s="3">
         <v>952100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-16852300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-22110600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-7679000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2002900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2048900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1648100</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3970200</v>
+      </c>
+      <c r="E15" s="3">
         <v>3032200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2960100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3395100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3643400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2953900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1893600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1279900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>845400</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -938,68 +963,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>61966100</v>
+        <v>72363300</v>
       </c>
       <c r="E17" s="3">
+        <v>61966500</v>
+      </c>
+      <c r="F17" s="3">
         <v>62904700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64326400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>68675500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54633800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40194300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34080100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25179400</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>28491200</v>
+        <v>35117800</v>
       </c>
       <c r="E18" s="3">
+        <v>28490800</v>
+      </c>
+      <c r="F18" s="3">
         <v>22982100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16076100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19496000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19205000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13991300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11384800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11361400</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1012,158 +1044,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-2789400</v>
+        <v>-2975000</v>
       </c>
       <c r="E20" s="3">
+        <v>-3090800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-372600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2246700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2462000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-495400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>230400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-249500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-149500</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>34312700</v>
+        <v>42062900</v>
       </c>
       <c r="E21" s="3">
+        <v>34613700</v>
+      </c>
+      <c r="F21" s="3">
         <v>26314900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17224500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20677400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22654300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15654500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12914200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12356300</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1923800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1705300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1676100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1447700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1246400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1141000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1104400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>712200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>470300</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>39638700</v>
+      </c>
+      <c r="E23" s="3">
         <v>33084200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22750800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30479800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>39048900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27574400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15711800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13735100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13557600</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>6783700</v>
+      </c>
+      <c r="E24" s="3">
         <v>6167600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6103000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3119500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3188000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3047700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1940600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2105600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2419700</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1191,69 +1239,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>32855000</v>
+      </c>
+      <c r="E26" s="3">
         <v>26916600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16647800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27360200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35860900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24526700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13771300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11629500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11137900</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>32146000</v>
+      </c>
+      <c r="E27" s="3">
         <v>26588600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16248400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27292700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>35390600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24484100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13401000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11445500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10990200</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1281,9 +1338,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1311,9 +1371,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1341,9 +1404,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1371,69 +1437,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>2789400</v>
+        <v>2975000</v>
       </c>
       <c r="E32" s="3">
+        <v>3090800</v>
+      </c>
+      <c r="F32" s="3">
         <v>372600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2246700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2462000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>495400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-230400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>249500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>149500</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>32146000</v>
+      </c>
+      <c r="E33" s="3">
         <v>26588600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16248400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27292700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35390500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24484100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13401000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11445500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10990200</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1461,74 +1536,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>32146000</v>
+      </c>
+      <c r="E35" s="3">
         <v>26588600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16248400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27292700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35390500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24484100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13401000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11445500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10990200</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1541,8 +1625,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1555,278 +1640,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>20164800</v>
+      </c>
+      <c r="E41" s="3">
         <v>18155500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24301600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22725000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26440500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23404400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19099900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14221900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16244300</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>28858400</v>
+        <v>40248100</v>
       </c>
       <c r="E42" s="3">
+        <v>28207600</v>
+      </c>
+      <c r="F42" s="3">
         <v>29169100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19430600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15133200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11673700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7812800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10095200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5644000</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>11572700</v>
+        <v>13593700</v>
       </c>
       <c r="E43" s="3">
+        <v>11267400</v>
+      </c>
+      <c r="F43" s="3">
         <v>11320600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10347200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10816200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8108000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5851300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4594900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3162000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E44" s="3">
         <v>60300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>64300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>338300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>167300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>124700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>103100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>47100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>45300</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>6499700</v>
+        <v>7447800</v>
       </c>
       <c r="E45" s="3">
+        <v>7455700</v>
+      </c>
+      <c r="F45" s="3">
         <v>5439600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26505100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20883700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2737000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1730500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1466800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1453100</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>85133800</v>
+      </c>
+      <c r="E46" s="3">
         <v>67978200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73114300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>82060700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>76317100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>48654700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36474500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31562900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27425000</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>121035600</v>
+        <v>140514000</v>
       </c>
       <c r="E47" s="3">
+        <v>120888200</v>
+      </c>
+      <c r="F47" s="3">
         <v>101339600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>98499400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>123788800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>109667900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64834600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>53027000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>42802800</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>25297700</v>
+      </c>
+      <c r="E48" s="3">
         <v>15093100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12308600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12429800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13900600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11903200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8847800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5811500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4112700</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>32645800</v>
+      </c>
+      <c r="E49" s="3">
         <v>30037100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27486800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26075500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>29768000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26886000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20748400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9270000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6973900</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1854,9 +1967,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1884,39 +2000,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>5515100</v>
+        <v>3281100</v>
       </c>
       <c r="E52" s="3">
+        <v>5662500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3573900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4714200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5294800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3696800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3354900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2674100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2110600</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1944,39 +2066,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>291516900</v>
+      </c>
+      <c r="E54" s="3">
         <v>244002000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>222432400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>228807500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>253811700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>204243600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137009900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105198100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>85246300</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1989,8 +2117,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2003,188 +2132,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>17317700</v>
+      </c>
+      <c r="E57" s="3">
         <v>16263900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14236300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13394000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17232300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14402800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11588600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10720900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7697500</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>8370400</v>
+      </c>
+      <c r="E58" s="3">
         <v>9194000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8722700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4114700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3848700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2766900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5243200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5896400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3142600</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>25236900</v>
+      </c>
+      <c r="E59" s="3">
         <v>22300800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19863500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39245600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>35561500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18137300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13450400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9527700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9351700</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>59011600</v>
+      </c>
+      <c r="E60" s="3">
         <v>54377800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49663200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62953700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63454000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41215400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34490800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29433500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23320600</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>49733100</v>
+      </c>
+      <c r="E61" s="3">
         <v>39868500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43631700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47955800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47127900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37732000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28221900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20171700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17129600</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1919100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1973400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2954500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2122700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2443100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2638700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1195600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1178200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>924600</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2212,9 +2360,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2242,9 +2393,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2272,39 +2426,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>114080000</v>
+      </c>
+      <c r="E66" s="3">
         <v>99614900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99220800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>115303500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>115806300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85069100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66805800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53406500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42660500</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2317,8 +2477,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2346,9 +2507,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2376,9 +2540,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2406,9 +2573,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2436,39 +2606,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>145907400</v>
+      </c>
+      <c r="E72" s="3">
         <v>123357100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>115758800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>103229100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>106230500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>83130200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55749000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>43975500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31499100</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2496,9 +2672,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2526,9 +2705,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2556,39 +2738,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>165010900</v>
+      </c>
+      <c r="E76" s="3">
         <v>133379200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>114032200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>104591900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>126924300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>107830800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62144500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47037500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>39355400</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2616,74 +2804,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>32146000</v>
+      </c>
+      <c r="E81" s="3">
         <v>26588600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16248400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27292700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35390500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24484100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13401000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11445500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10990200</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2696,38 +2893,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>4689300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3744600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3709700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4124000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4118900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3286800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2243700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1224700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>750000</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2755,9 +2956,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2785,9 +2989,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2815,9 +3022,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2845,9 +3055,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2875,39 +3088,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>43327800</v>
+      </c>
+      <c r="E89" s="3">
         <v>35418200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31302400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21181200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27577100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29733600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21340200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16129800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16312400</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2920,38 +3139,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-12507400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8621200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2962700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3288100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4612600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5218600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3269600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2870600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1860900</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2979,9 +3202,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3009,39 +3235,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-29413800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16740000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17650900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15204900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-28106400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27870400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16684100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22087800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14814300</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3054,38 +3286,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>5366400</v>
+      </c>
+      <c r="E96" s="3">
         <v>3953800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2959100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1877900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1968200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1583600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1194200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>985200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>776400</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3113,9 +3349,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3143,9 +3382,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3173,97 +3415,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-12460700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24180200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11644900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8692400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3403300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2090300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>240100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4490900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4087800</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-234900</v>
+      </c>
+      <c r="E101" s="3">
         <v>49200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>190800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1088300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-486300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-919600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>155800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>320900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-392100</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1218400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5452900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2197300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1627800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2387700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3033900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5052100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1146200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5193900</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
